--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N85_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.65594711709915</v>
+        <v>12.78159140652861</v>
       </c>
       <c r="D2" t="n">
-        <v>3.970318684241176</v>
+        <v>0.6451767861891912</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
